--- a/backend/licenses.xlsx
+++ b/backend/licenses.xlsx
@@ -11,21 +11,270 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Doctor Name</t>
-  </si>
-  <si>
-    <t>License Type</t>
-  </si>
-  <si>
-    <t>License Number</t>
-  </si>
-  <si>
-    <t>Expiry Date</t>
-  </si>
-  <si>
-    <t>Notification Email</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Provider Name</t>
+  </si>
+  <si>
+    <t>Provider Tax ID / NPI</t>
+  </si>
+  <si>
+    <t>Credential Type</t>
+  </si>
+  <si>
+    <t>Provider Number</t>
+  </si>
+  <si>
+    <t>Issuing Authority</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Expiration Date</t>
+  </si>
+  <si>
+    <t>Renewal Due Date</t>
+  </si>
+  <si>
+    <t>Reminder Schedule</t>
+  </si>
+  <si>
+    <t>Responsible Person</t>
+  </si>
+  <si>
+    <t>Coordinator Email</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Renewal Submitted Date</t>
+  </si>
+  <si>
+    <t>Renewal Completed Date</t>
+  </si>
+  <si>
+    <t>Last Reminder Sent</t>
+  </si>
+  <si>
+    <t>Next Reminder Date</t>
+  </si>
+  <si>
+    <t>Created At</t>
+  </si>
+  <si>
+    <t>LIC-1001</t>
+  </si>
+  <si>
+    <t>Dr. Alexander Wright</t>
+  </si>
+  <si>
+    <t>1827493012</t>
+  </si>
+  <si>
+    <t>State Medical License</t>
+  </si>
+  <si>
+    <t>MD-749201</t>
+  </si>
+  <si>
+    <t>State Medical Board</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>60 days</t>
+  </si>
+  <si>
+    <t>Sarah Jenkins</t>
+  </si>
+  <si>
+    <t>sjenkins@clinic.org</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
+  </si>
+  <si>
+    <t>2026-08-06T14:23:11.086Z</t>
+  </si>
+  <si>
+    <t>LIC-1002</t>
+  </si>
+  <si>
+    <t>Dr. Elena Rostova</t>
+  </si>
+  <si>
+    <t>1938204958</t>
+  </si>
+  <si>
+    <t>DEA Registration</t>
+  </si>
+  <si>
+    <t>DEA-839201</t>
+  </si>
+  <si>
+    <t>Drug Enforcement Administration</t>
+  </si>
+  <si>
+    <t>2022-03-10</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>30 days</t>
+  </si>
+  <si>
+    <t>Michael Chang</t>
+  </si>
+  <si>
+    <t>mchang@healthsystem.com</t>
+  </si>
+  <si>
+    <t>Pending Renewal</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-08-06T14:23:11.087Z</t>
+  </si>
+  <si>
+    <t>LIC-1003</t>
+  </si>
+  <si>
+    <t>Dr. Marcus Vance</t>
+  </si>
+  <si>
+    <t>1029384756</t>
+  </si>
+  <si>
+    <t>Medicare ID</t>
+  </si>
+  <si>
+    <t>MED-409281</t>
+  </si>
+  <si>
+    <t>Medicare / CMS</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>15 days</t>
+  </si>
+  <si>
+    <t>Rachel Adams</t>
+  </si>
+  <si>
+    <t>radams@medicalcenter.org</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>LIC-1004</t>
+  </si>
+  <si>
+    <t>Dr. Sophia Patel</t>
+  </si>
+  <si>
+    <t>1492038471</t>
+  </si>
+  <si>
+    <t>Board Certification</t>
+  </si>
+  <si>
+    <t>BC-920412</t>
+  </si>
+  <si>
+    <t>American Board of Internal Medicine</t>
+  </si>
+  <si>
+    <t>2019-09-20</t>
+  </si>
+  <si>
+    <t>2027-09-20</t>
+  </si>
+  <si>
+    <t>2027-08-20</t>
+  </si>
+  <si>
+    <t>90 days</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2027-06-20</t>
+  </si>
+  <si>
+    <t>LIC-1786027084222</t>
+  </si>
+  <si>
+    <t>Dr. Emily Carter</t>
+  </si>
+  <si>
+    <t>1982736405</t>
+  </si>
+  <si>
+    <t>MD-987654</t>
+  </si>
+  <si>
+    <t>State Medical Board of California</t>
+  </si>
+  <si>
+    <t>2024-03-15</t>
+  </si>
+  <si>
+    <t>2027-03-15</t>
+  </si>
+  <si>
+    <t>2027-02-15</t>
+  </si>
+  <si>
+    <t>Sarah Johnson</t>
+  </si>
+  <si>
+    <t>sarah.johnson@healthfirstclinic.com</t>
+  </si>
+  <si>
+    <t>2026-08-06T14:38:04.222Z</t>
   </si>
 </sst>
 </file>
@@ -43,6 +292,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,8 +304,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D4ED8"/>
-        <bgColor rgb="FF1D4ED8"/>
+        <fgColor rgb="FF1E293B"/>
+        <bgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
@@ -415,16 +665,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="6" width="24" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="15" width="22" customWidth="1"/>
+    <col min="16" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,10 +696,329 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>